--- a/app/templates/Template_ContHumedad.xlsx
+++ b/app/templates/Template_ContHumedad.xlsx
@@ -9795,7 +9795,6 @@
       <c r="H61" s="480"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="E4saOIWIh+Eme1oJwQuMKDkpQOD3mu/gNSXXqxi1z9FTNqSBh3K6FNpoNItb60yc5uGoFN6+zjqUl8BeksL6fA==" saltValue="903QStExJ+2hr453WB5skg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="13">
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="E59:F59"/>
